--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/26.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/26.xlsx
@@ -426,13 +426,13 @@
         <v>-11.45675651152844</v>
       </c>
       <c r="E2">
-        <v>-11.43103987968484</v>
+        <v>-8.369915472719958</v>
       </c>
       <c r="F2">
-        <v>2.55237460629976</v>
+        <v>2.349081648509122</v>
       </c>
       <c r="G2">
-        <v>-17.12198696597588</v>
+        <v>-18.37115515197504</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.84125443141458</v>
       </c>
       <c r="E3">
-        <v>-10.60733347763159</v>
+        <v>-9.356656185329348</v>
       </c>
       <c r="F3">
-        <v>2.775434067056</v>
+        <v>2.258037444002234</v>
       </c>
       <c r="G3">
-        <v>-16.99813063182888</v>
+        <v>-17.80704373593941</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.09972947292549</v>
       </c>
       <c r="E4">
-        <v>-11.64524175376287</v>
+        <v>-9.903916535179356</v>
       </c>
       <c r="F4">
-        <v>2.227551866844407</v>
+        <v>2.079322147052657</v>
       </c>
       <c r="G4">
-        <v>-16.59483586111665</v>
+        <v>-17.40120871074004</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.322235753557907</v>
       </c>
       <c r="E5">
-        <v>-11.33807024417855</v>
+        <v>-10.47421474824819</v>
       </c>
       <c r="F5">
-        <v>3.177381125181598</v>
+        <v>2.247223935926089</v>
       </c>
       <c r="G5">
-        <v>-15.86145420877161</v>
+        <v>-16.83166825132719</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.545389774775261</v>
       </c>
       <c r="E6">
-        <v>-12.60246974669803</v>
+        <v>-10.19307556724789</v>
       </c>
       <c r="F6">
-        <v>2.867217175286185</v>
+        <v>2.387663688661912</v>
       </c>
       <c r="G6">
-        <v>-15.28388048825191</v>
+        <v>-15.91895324764629</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.80635875027343</v>
       </c>
       <c r="E7">
-        <v>-14.12605870836608</v>
+        <v>-11.73285374666013</v>
       </c>
       <c r="F7">
-        <v>2.683819945775985</v>
+        <v>2.443609966312185</v>
       </c>
       <c r="G7">
-        <v>-15.10441007282501</v>
+        <v>-15.59716722844091</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.140072614165727</v>
       </c>
       <c r="E8">
-        <v>-13.61211957297517</v>
+        <v>-12.36321985511995</v>
       </c>
       <c r="F8">
-        <v>2.685541293239003</v>
+        <v>2.486749683915177</v>
       </c>
       <c r="G8">
-        <v>-13.79968915804385</v>
+        <v>-15.28265213292179</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.558181060349072</v>
       </c>
       <c r="E9">
-        <v>-13.95573966514618</v>
+        <v>-12.75754235114447</v>
       </c>
       <c r="F9">
-        <v>3.06913338645337</v>
+        <v>2.372907151748441</v>
       </c>
       <c r="G9">
-        <v>-14.46879950004486</v>
+        <v>-14.94942713629046</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.077479910863111</v>
       </c>
       <c r="E10">
-        <v>-15.68944374094863</v>
+        <v>-12.83872101969957</v>
       </c>
       <c r="F10">
-        <v>3.233030847301669</v>
+        <v>2.437054266686429</v>
       </c>
       <c r="G10">
-        <v>-13.76736291851669</v>
+        <v>-14.34225279359672</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.68736486199344</v>
       </c>
       <c r="E11">
-        <v>-14.45500550492647</v>
+        <v>-13.96925421479717</v>
       </c>
       <c r="F11">
-        <v>3.215429696726985</v>
+        <v>3.032082169260954</v>
       </c>
       <c r="G11">
-        <v>-13.43030534882559</v>
+        <v>-14.15844201528709</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.389377635660789</v>
       </c>
       <c r="E12">
-        <v>-16.36476836199973</v>
+        <v>-14.22712295274445</v>
       </c>
       <c r="F12">
-        <v>3.728719274197671</v>
+        <v>3.333816652465479</v>
       </c>
       <c r="G12">
-        <v>-12.36195602783465</v>
+        <v>-13.58537052381477</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.158027571890717</v>
       </c>
       <c r="E13">
-        <v>-18.12160582488148</v>
+        <v>-15.29546596146407</v>
       </c>
       <c r="F13">
-        <v>4.051010522870069</v>
+        <v>3.108535510334931</v>
       </c>
       <c r="G13">
-        <v>-12.41442024576537</v>
+        <v>-13.25369761484285</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.984986708061102</v>
       </c>
       <c r="E14">
-        <v>-17.24924039894654</v>
+        <v>-15.27158914955763</v>
       </c>
       <c r="F14">
-        <v>3.960408666556275</v>
+        <v>3.171847630930897</v>
       </c>
       <c r="G14">
-        <v>-11.2189890156851</v>
+        <v>-12.88151378205063</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.83891840266063</v>
       </c>
       <c r="E15">
-        <v>-18.68011307099912</v>
+        <v>-17.1316380670727</v>
       </c>
       <c r="F15">
-        <v>4.087919260869203</v>
+        <v>3.580338791538612</v>
       </c>
       <c r="G15">
-        <v>-11.73326131747636</v>
+        <v>-12.5560139786644</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.706820481862646</v>
       </c>
       <c r="E16">
-        <v>-19.43072710694671</v>
+        <v>-17.73600091942777</v>
       </c>
       <c r="F16">
-        <v>4.092013052573838</v>
+        <v>3.811068934444775</v>
       </c>
       <c r="G16">
-        <v>-10.6119204081473</v>
+        <v>-12.22666854849546</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.559632811754763</v>
       </c>
       <c r="E17">
-        <v>-19.92278297186709</v>
+        <v>-18.27544077235313</v>
       </c>
       <c r="F17">
-        <v>4.874321571042886</v>
+        <v>3.982542643559078</v>
       </c>
       <c r="G17">
-        <v>-10.26424494020415</v>
+        <v>-12.39249129657231</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.38749562744799</v>
       </c>
       <c r="E18">
-        <v>-19.95376177513899</v>
+        <v>-19.94463301664702</v>
       </c>
       <c r="F18">
-        <v>4.535285703690299</v>
+        <v>4.238289482029787</v>
       </c>
       <c r="G18">
-        <v>-9.800856050493678</v>
+        <v>-11.75733107723413</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.172155407733867</v>
       </c>
       <c r="E19">
-        <v>-22.01340987571399</v>
+        <v>-21.56895396578746</v>
       </c>
       <c r="F19">
-        <v>4.778124921290585</v>
+        <v>4.386086794037274</v>
       </c>
       <c r="G19">
-        <v>-9.89672520262395</v>
+        <v>-11.26480497251454</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.914162968601377</v>
       </c>
       <c r="E20">
-        <v>-22.2775582691844</v>
+        <v>-21.16830612891522</v>
       </c>
       <c r="F20">
-        <v>4.981984482384738</v>
+        <v>4.728790672249458</v>
       </c>
       <c r="G20">
-        <v>-9.549844706408797</v>
+        <v>-11.36761609451258</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.609358093482237</v>
       </c>
       <c r="E21">
-        <v>-22.4919553441947</v>
+        <v>-22.03419669839475</v>
       </c>
       <c r="F21">
-        <v>5.364857552693475</v>
+        <v>4.779122275643555</v>
       </c>
       <c r="G21">
-        <v>-9.820902652836542</v>
+        <v>-10.55053527594874</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.269045332455687</v>
       </c>
       <c r="E22">
-        <v>-23.40665860637494</v>
+        <v>-22.75284346677513</v>
       </c>
       <c r="F22">
-        <v>5.156228252094002</v>
+        <v>4.977902287823742</v>
       </c>
       <c r="G22">
-        <v>-9.408685662484189</v>
+        <v>-10.28335167449421</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.899683981402707</v>
       </c>
       <c r="E23">
-        <v>-23.96035228056711</v>
+        <v>-23.04710679556188</v>
       </c>
       <c r="F23">
-        <v>5.939578856755772</v>
+        <v>4.734547825698914</v>
       </c>
       <c r="G23">
-        <v>-9.313424813843646</v>
+        <v>-10.14108959097986</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.518403421047197</v>
       </c>
       <c r="E24">
-        <v>-24.53235331027912</v>
+        <v>-23.640870652616</v>
       </c>
       <c r="F24">
-        <v>5.481885985891378</v>
+        <v>5.124129015235522</v>
       </c>
       <c r="G24">
-        <v>-8.29408439031708</v>
+        <v>-9.99765658851639</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.133600273058356</v>
       </c>
       <c r="E25">
-        <v>-25.22372178667803</v>
+        <v>-24.30294652954089</v>
       </c>
       <c r="F25">
-        <v>5.082271610372063</v>
+        <v>4.738318554116457</v>
       </c>
       <c r="G25">
-        <v>-8.641617572680012</v>
+        <v>-9.775672808167799</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.759597657753369</v>
       </c>
       <c r="E26">
-        <v>-25.03807739366952</v>
+        <v>-25.14432899899261</v>
       </c>
       <c r="F26">
-        <v>5.796130473612982</v>
+        <v>4.632184809000174</v>
       </c>
       <c r="G26">
-        <v>-8.437662289105354</v>
+        <v>-9.921438510923428</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.400521465394351</v>
       </c>
       <c r="E27">
-        <v>-24.20759710394548</v>
+        <v>-25.33276850322273</v>
       </c>
       <c r="F27">
-        <v>5.140431285722616</v>
+        <v>5.126206560681743</v>
       </c>
       <c r="G27">
-        <v>-8.484596949992094</v>
+        <v>-9.194776915155911</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.064945204144696</v>
       </c>
       <c r="E28">
-        <v>-26.51749279968669</v>
+        <v>-25.89711101125175</v>
       </c>
       <c r="F28">
-        <v>5.228251484297808</v>
+        <v>4.666147872514953</v>
       </c>
       <c r="G28">
-        <v>-8.11867368272936</v>
+        <v>-8.932382724653776</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.7530560221519753</v>
       </c>
       <c r="E29">
-        <v>-25.8808428824924</v>
+        <v>-26.47588177542324</v>
       </c>
       <c r="F29">
-        <v>5.124465332401059</v>
+        <v>4.747574731475339</v>
       </c>
       <c r="G29">
-        <v>-7.481308689583987</v>
+        <v>-8.834868803431103</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.4703571060115945</v>
       </c>
       <c r="E30">
-        <v>-26.45171008551273</v>
+        <v>-26.66614038621363</v>
       </c>
       <c r="F30">
-        <v>4.966528803383304</v>
+        <v>4.526904282308774</v>
       </c>
       <c r="G30">
-        <v>-7.731737837625051</v>
+        <v>-8.518522270581315</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.2168646077280702</v>
       </c>
       <c r="E31">
-        <v>-25.62546191812869</v>
+        <v>-27.18574865506293</v>
       </c>
       <c r="F31">
-        <v>5.060107812142759</v>
+        <v>4.497497239509391</v>
       </c>
       <c r="G31">
-        <v>-8.14239360271192</v>
+        <v>-8.150113574467841</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.0002618070749020543</v>
       </c>
       <c r="E32">
-        <v>-26.89141472168366</v>
+        <v>-26.57339087090756</v>
       </c>
       <c r="F32">
-        <v>5.052682326744065</v>
+        <v>4.27288707497511</v>
       </c>
       <c r="G32">
-        <v>-7.533899528627373</v>
+        <v>-8.017453809559603</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.1758234660405862</v>
       </c>
       <c r="E33">
-        <v>-26.19210115202035</v>
+        <v>-28.01631200901346</v>
       </c>
       <c r="F33">
-        <v>5.579305305930211</v>
+        <v>4.277219436491752</v>
       </c>
       <c r="G33">
-        <v>-6.886541910559513</v>
+        <v>-8.408974122165906</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.3038033831528674</v>
       </c>
       <c r="E34">
-        <v>-27.08965165142905</v>
+        <v>-27.18538732567767</v>
       </c>
       <c r="F34">
-        <v>4.46621477291007</v>
+        <v>4.42781000338148</v>
       </c>
       <c r="G34">
-        <v>-7.980409954556296</v>
+        <v>-7.58077022627163</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.3816912989014365</v>
       </c>
       <c r="E35">
-        <v>-24.90606757170984</v>
+        <v>-27.06253948790057</v>
       </c>
       <c r="F35">
-        <v>4.66951104417032</v>
+        <v>4.75989918169419</v>
       </c>
       <c r="G35">
-        <v>-6.898788913436426</v>
+        <v>-7.412298877807089</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.4058996941629134</v>
       </c>
       <c r="E36">
-        <v>-25.52090482302614</v>
+        <v>-26.52743558759833</v>
       </c>
       <c r="F36">
-        <v>4.887850467465407</v>
+        <v>4.496072447576576</v>
       </c>
       <c r="G36">
-        <v>-7.222069583920211</v>
+        <v>-7.299013448509502</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.3779343967981169</v>
       </c>
       <c r="E37">
-        <v>-25.29483722419307</v>
+        <v>-26.29535413876691</v>
       </c>
       <c r="F37">
-        <v>5.027228253190841</v>
+        <v>4.352827842814874</v>
       </c>
       <c r="G37">
-        <v>-7.926229172056922</v>
+        <v>-7.467892073130256</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3001503742335591</v>
       </c>
       <c r="E38">
-        <v>-24.74942090017128</v>
+        <v>-26.75357379102392</v>
       </c>
       <c r="F38">
-        <v>5.249424555113364</v>
+        <v>4.649789273044469</v>
       </c>
       <c r="G38">
-        <v>-7.399362638358123</v>
+        <v>-7.657580942886773</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1784324771116879</v>
       </c>
       <c r="E39">
-        <v>-25.48427765235247</v>
+        <v>-27.24680501474923</v>
       </c>
       <c r="F39">
-        <v>5.658831890068575</v>
+        <v>4.811735100291772</v>
       </c>
       <c r="G39">
-        <v>-7.281200338164336</v>
+        <v>-7.142133806029505</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.01980356521427427</v>
       </c>
       <c r="E40">
-        <v>-24.9191418809604</v>
+        <v>-26.28293188369435</v>
       </c>
       <c r="F40">
-        <v>5.111524576834524</v>
+        <v>4.865035572457503</v>
       </c>
       <c r="G40">
-        <v>-7.419199075761401</v>
+        <v>-7.13227563445346</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1674076294228878</v>
       </c>
       <c r="E41">
-        <v>-23.78970098044123</v>
+        <v>-25.68788883755219</v>
       </c>
       <c r="F41">
-        <v>5.904333480501458</v>
+        <v>5.058248955690877</v>
       </c>
       <c r="G41">
-        <v>-7.446786813855696</v>
+        <v>-7.454279650832191</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3751343226449635</v>
       </c>
       <c r="E42">
-        <v>-23.60800629140263</v>
+        <v>-25.76884738590707</v>
       </c>
       <c r="F42">
-        <v>5.992031080701037</v>
+        <v>5.356235904765137</v>
       </c>
       <c r="G42">
-        <v>-6.91082966749064</v>
+        <v>-6.881518837966212</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.5965113048884592</v>
       </c>
       <c r="E43">
-        <v>-23.81081175360533</v>
+        <v>-25.94103952743447</v>
       </c>
       <c r="F43">
-        <v>5.070285134053554</v>
+        <v>5.445399715267671</v>
       </c>
       <c r="G43">
-        <v>-7.609759934211351</v>
+        <v>-7.589359575976393</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.8246711821764636</v>
       </c>
       <c r="E44">
-        <v>-22.16218205858067</v>
+        <v>-25.55952138192439</v>
       </c>
       <c r="F44">
-        <v>6.093554132853338</v>
+        <v>5.392824892946792</v>
       </c>
       <c r="G44">
-        <v>-6.859437160214576</v>
+        <v>-7.898473040936501</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.05593025407538</v>
       </c>
       <c r="E45">
-        <v>-23.71261322504109</v>
+        <v>-24.10733858256411</v>
       </c>
       <c r="F45">
-        <v>5.610596056203559</v>
+        <v>5.736594051638975</v>
       </c>
       <c r="G45">
-        <v>-7.909782786505204</v>
+        <v>-7.934254600930005</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.286110375753272</v>
       </c>
       <c r="E46">
-        <v>-22.88033874802472</v>
+        <v>-24.24547439122791</v>
       </c>
       <c r="F46">
-        <v>5.796909138971613</v>
+        <v>5.506829785124476</v>
       </c>
       <c r="G46">
-        <v>-7.928984812972842</v>
+        <v>-7.956837541643134</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.514528684509609</v>
       </c>
       <c r="E47">
-        <v>-22.18848434590081</v>
+        <v>-23.20223339175556</v>
       </c>
       <c r="F47">
-        <v>5.658664559853209</v>
+        <v>5.976320264539541</v>
       </c>
       <c r="G47">
-        <v>-8.399824767746349</v>
+        <v>-8.064592108524447</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.738959949934183</v>
       </c>
       <c r="E48">
-        <v>-21.52093453644979</v>
+        <v>-23.31321965798895</v>
       </c>
       <c r="F48">
-        <v>5.474293170277318</v>
+        <v>5.718797406357231</v>
       </c>
       <c r="G48">
-        <v>-8.627612233320983</v>
+        <v>-8.463179706738895</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.960881700900186</v>
       </c>
       <c r="E49">
-        <v>-21.05874856737757</v>
+        <v>-22.20059095691268</v>
       </c>
       <c r="F49">
-        <v>5.422157382679922</v>
+        <v>5.967077341059104</v>
       </c>
       <c r="G49">
-        <v>-8.01618237694373</v>
+        <v>-8.097731594991744</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.179491668787373</v>
       </c>
       <c r="E50">
-        <v>-20.42084438036318</v>
+        <v>-22.64584013020225</v>
       </c>
       <c r="F50">
-        <v>5.241556721521574</v>
+        <v>5.961638280692322</v>
       </c>
       <c r="G50">
-        <v>-8.453406384362063</v>
+        <v>-8.483838528688375</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.397331639081224</v>
       </c>
       <c r="E51">
-        <v>-19.16802403101733</v>
+        <v>-22.27185175682409</v>
       </c>
       <c r="F51">
-        <v>6.085848659272497</v>
+        <v>5.908023028913528</v>
       </c>
       <c r="G51">
-        <v>-8.289091341286575</v>
+        <v>-8.756643063247576</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.614092737507149</v>
       </c>
       <c r="E52">
-        <v>-18.66159805491304</v>
+        <v>-21.18912617728659</v>
       </c>
       <c r="F52">
-        <v>5.755586859450363</v>
+        <v>6.024791354746951</v>
       </c>
       <c r="G52">
-        <v>-9.577705267312862</v>
+        <v>-8.894640495472347</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.831994679460839</v>
       </c>
       <c r="E53">
-        <v>-20.59239277413522</v>
+        <v>-21.41459571368888</v>
       </c>
       <c r="F53">
-        <v>5.186163793296371</v>
+        <v>5.785971375785048</v>
       </c>
       <c r="G53">
-        <v>-9.754681116282955</v>
+        <v>-9.658238905714933</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.049015331248385</v>
       </c>
       <c r="E54">
-        <v>-18.43030156302201</v>
+        <v>-20.6383397510218</v>
       </c>
       <c r="F54">
-        <v>5.512625043474462</v>
+        <v>6.094087601460741</v>
       </c>
       <c r="G54">
-        <v>-9.382703532313428</v>
+        <v>-9.575154569847344</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.266233328006704</v>
       </c>
       <c r="E55">
-        <v>-18.84625813683756</v>
+        <v>-20.30973767100137</v>
       </c>
       <c r="F55">
-        <v>5.764215134317922</v>
+        <v>6.210627297890992</v>
       </c>
       <c r="G55">
-        <v>-9.135552174106508</v>
+        <v>-9.226175034980935</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.48093380832668</v>
       </c>
       <c r="E56">
-        <v>-17.10993338468914</v>
+        <v>-19.4643141269306</v>
       </c>
       <c r="F56">
-        <v>5.753986453628154</v>
+        <v>6.072801872678405</v>
       </c>
       <c r="G56">
-        <v>-9.170433027216076</v>
+        <v>-9.166116161034671</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.693845804809814</v>
       </c>
       <c r="E57">
-        <v>-18.82203660839116</v>
+        <v>-19.34412849761271</v>
       </c>
       <c r="F57">
-        <v>5.723880268740809</v>
+        <v>6.066541071848047</v>
       </c>
       <c r="G57">
-        <v>-9.461673334705424</v>
+        <v>-9.965878605353359</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.901768194335708</v>
       </c>
       <c r="E58">
-        <v>-17.99120329570451</v>
+        <v>-19.0354369126835</v>
       </c>
       <c r="F58">
-        <v>6.292985241812125</v>
+        <v>6.18259037477584</v>
       </c>
       <c r="G58">
-        <v>-10.65831986639286</v>
+        <v>-10.11689190473713</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.105192046638658</v>
       </c>
       <c r="E59">
-        <v>-16.51931766181925</v>
+        <v>-18.39922308267831</v>
       </c>
       <c r="F59">
-        <v>5.739890953902117</v>
+        <v>6.554080020235307</v>
       </c>
       <c r="G59">
-        <v>-9.564754668768645</v>
+        <v>-10.25109984118789</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.300154858782106</v>
       </c>
       <c r="E60">
-        <v>-17.21044940517264</v>
+        <v>-18.10471056121207</v>
       </c>
       <c r="F60">
-        <v>5.935206733603796</v>
+        <v>6.488367290906027</v>
       </c>
       <c r="G60">
-        <v>-9.922961880392343</v>
+        <v>-10.25999073189293</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.487019288550313</v>
       </c>
       <c r="E61">
-        <v>-17.61498049463359</v>
+        <v>-17.39002595643558</v>
       </c>
       <c r="F61">
-        <v>6.247661947735352</v>
+        <v>6.310926023021956</v>
       </c>
       <c r="G61">
-        <v>-10.30234092527767</v>
+        <v>-10.27459132101873</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.662209180698885</v>
       </c>
       <c r="E62">
-        <v>-16.12067582601691</v>
+        <v>-17.81797285134591</v>
       </c>
       <c r="F62">
-        <v>6.115926679668148</v>
+        <v>6.244862065913891</v>
       </c>
       <c r="G62">
-        <v>-10.76753906098979</v>
+        <v>-10.37681763622836</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.827627781784476</v>
       </c>
       <c r="E63">
-        <v>-15.63117418606129</v>
+        <v>-17.14763623709593</v>
       </c>
       <c r="F63">
-        <v>5.765136278869835</v>
+        <v>6.523392321431196</v>
       </c>
       <c r="G63">
-        <v>-10.54203077544319</v>
+        <v>-10.1493330170263</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.980531346448843</v>
       </c>
       <c r="E64">
-        <v>-15.16537492313647</v>
+        <v>-16.75394087598146</v>
       </c>
       <c r="F64">
-        <v>5.826854620582815</v>
+        <v>6.329458258557387</v>
       </c>
       <c r="G64">
-        <v>-10.70273515874917</v>
+        <v>-10.90498954222272</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.123885009097611</v>
       </c>
       <c r="E65">
-        <v>-14.79836809799535</v>
+        <v>-17.46801911190454</v>
       </c>
       <c r="F65">
-        <v>5.630017958329597</v>
+        <v>6.448718313538432</v>
       </c>
       <c r="G65">
-        <v>-10.72898358486822</v>
+        <v>-10.85604330262853</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.25523025571264</v>
       </c>
       <c r="E66">
-        <v>-14.72050784528879</v>
+        <v>-16.26213835695189</v>
       </c>
       <c r="F66">
-        <v>5.322566083310948</v>
+        <v>6.408529240624211</v>
       </c>
       <c r="G66">
-        <v>-10.55285492251795</v>
+        <v>-11.13038817649648</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.378475879264506</v>
       </c>
       <c r="E67">
-        <v>-16.15918024820939</v>
+        <v>-16.76007516910823</v>
       </c>
       <c r="F67">
-        <v>6.501379286069202</v>
+        <v>6.553995526760221</v>
       </c>
       <c r="G67">
-        <v>-10.61138781625071</v>
+        <v>-11.58475955438925</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.491547965817999</v>
       </c>
       <c r="E68">
-        <v>-15.16482254603027</v>
+        <v>-17.00167162508484</v>
       </c>
       <c r="F68">
-        <v>5.972261264265823</v>
+        <v>6.447033414241138</v>
       </c>
       <c r="G68">
-        <v>-11.01905036266387</v>
+        <v>-11.31921027904875</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.600026671754611</v>
       </c>
       <c r="E69">
-        <v>-14.94694507992976</v>
+        <v>-15.52164154379159</v>
       </c>
       <c r="F69">
-        <v>5.797629818612048</v>
+        <v>6.558003168254965</v>
       </c>
       <c r="G69">
-        <v>-11.11602777587307</v>
+        <v>-11.62651710875181</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.70315062793633</v>
       </c>
       <c r="E70">
-        <v>-15.19701408700901</v>
+        <v>-15.73980142826218</v>
       </c>
       <c r="F70">
-        <v>5.957030901197951</v>
+        <v>6.814641330051086</v>
       </c>
       <c r="G70">
-        <v>-10.92386392024417</v>
+        <v>-11.13881304929201</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.808170801118766</v>
       </c>
       <c r="E71">
-        <v>-15.17098591163631</v>
+        <v>-16.68854441046071</v>
       </c>
       <c r="F71">
-        <v>5.868761727490442</v>
+        <v>6.606669753169436</v>
       </c>
       <c r="G71">
-        <v>-10.24636264512732</v>
+        <v>-11.9480041977015</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.913832944962737</v>
       </c>
       <c r="E72">
-        <v>-16.15693336088266</v>
+        <v>-15.37614624466019</v>
       </c>
       <c r="F72">
-        <v>5.912386868391475</v>
+        <v>6.724065981494182</v>
       </c>
       <c r="G72">
-        <v>-11.06590931195746</v>
+        <v>-11.54968550617994</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.026968636479779</v>
       </c>
       <c r="E73">
-        <v>-14.41806269019212</v>
+        <v>-16.40582285594566</v>
       </c>
       <c r="F73">
-        <v>5.745154400379506</v>
+        <v>6.590612679433571</v>
       </c>
       <c r="G73">
-        <v>-10.13697897362115</v>
+        <v>-11.82822454123352</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.144689444179221</v>
       </c>
       <c r="E74">
-        <v>-16.03570527552224</v>
+        <v>-15.66227343246161</v>
       </c>
       <c r="F74">
-        <v>5.692771759296076</v>
+        <v>6.417283427336996</v>
       </c>
       <c r="G74">
-        <v>-11.20866482619954</v>
+        <v>-11.57454893229341</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.27362236457257</v>
       </c>
       <c r="E75">
-        <v>-15.7417783568528</v>
+        <v>-15.66850324944885</v>
       </c>
       <c r="F75">
-        <v>5.151627499538854</v>
+        <v>6.590980474560413</v>
       </c>
       <c r="G75">
-        <v>-10.94186108808301</v>
+        <v>-11.96481869824057</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.409303088812789</v>
       </c>
       <c r="E76">
-        <v>-15.67310085438543</v>
+        <v>-16.23991036994141</v>
       </c>
       <c r="F76">
-        <v>5.362869470926756</v>
+        <v>6.464977508920581</v>
       </c>
       <c r="G76">
-        <v>-11.69432206189991</v>
+        <v>-11.95538868877746</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.556915945412058</v>
       </c>
       <c r="E77">
-        <v>-16.24117294618416</v>
+        <v>-17.09135191722186</v>
       </c>
       <c r="F77">
-        <v>5.585589301047848</v>
+        <v>6.473628978075419</v>
       </c>
       <c r="G77">
-        <v>-10.91946873172503</v>
+        <v>-11.6385944132303</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.708947607152744</v>
       </c>
       <c r="E78">
-        <v>-15.62002696686545</v>
+        <v>-17.52511330798695</v>
       </c>
       <c r="F78">
-        <v>5.16197380839982</v>
+        <v>6.617736741670837</v>
       </c>
       <c r="G78">
-        <v>-10.62129559197398</v>
+        <v>-10.91475633773807</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.86835891951527</v>
       </c>
       <c r="E79">
-        <v>-17.70299119581803</v>
+        <v>-17.34698622747638</v>
       </c>
       <c r="F79">
-        <v>5.332796420735523</v>
+        <v>6.638368060204962</v>
       </c>
       <c r="G79">
-        <v>-10.47846175539418</v>
+        <v>-11.38625942163772</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.025053758477184</v>
       </c>
       <c r="E80">
-        <v>-16.52299325384172</v>
+        <v>-17.17851121008471</v>
       </c>
       <c r="F80">
-        <v>5.755060017782182</v>
+        <v>6.51908812440625</v>
       </c>
       <c r="G80">
-        <v>-10.04504812970657</v>
+        <v>-11.20542619753426</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.180265252700381</v>
       </c>
       <c r="E81">
-        <v>-17.17236445732397</v>
+        <v>-18.4891484142835</v>
       </c>
       <c r="F81">
-        <v>5.814164031971926</v>
+        <v>6.446880994639023</v>
       </c>
       <c r="G81">
-        <v>-10.26401519468013</v>
+        <v>-10.93253028691437</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.321713346569578</v>
       </c>
       <c r="E82">
-        <v>-19.1080350466415</v>
+        <v>-19.36004775662078</v>
       </c>
       <c r="F82">
-        <v>5.578652552416805</v>
+        <v>6.688398137864441</v>
       </c>
       <c r="G82">
-        <v>-10.42436712746631</v>
+        <v>-11.06030926480953</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.449360285808573</v>
       </c>
       <c r="E83">
-        <v>-19.19034338867695</v>
+        <v>-19.63702957308492</v>
       </c>
       <c r="F83">
-        <v>5.102833346044352</v>
+        <v>6.442812053956471</v>
       </c>
       <c r="G83">
-        <v>-9.574645474652078</v>
+        <v>-11.36658485039909</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.550682500874468</v>
       </c>
       <c r="E84">
-        <v>-20.67451006844973</v>
+        <v>-21.41842082131905</v>
       </c>
       <c r="F84">
-        <v>5.555902270066319</v>
+        <v>6.460764432309943</v>
       </c>
       <c r="G84">
-        <v>-8.444057307981286</v>
+        <v>-10.55582464449034</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.628336960500272</v>
       </c>
       <c r="E85">
-        <v>-22.1190634186063</v>
+        <v>-21.29328871731329</v>
       </c>
       <c r="F85">
-        <v>5.910753327873155</v>
+        <v>6.622564466894353</v>
       </c>
       <c r="G85">
-        <v>-10.09078837494288</v>
+        <v>-10.71795710508766</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.67356322583409</v>
       </c>
       <c r="E86">
-        <v>-23.10678428908835</v>
+        <v>-22.20330715711912</v>
       </c>
       <c r="F86">
-        <v>5.528803058851136</v>
+        <v>6.719375765259532</v>
       </c>
       <c r="G86">
-        <v>-10.14768302644471</v>
+        <v>-10.9994749997197</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.692120259220443</v>
       </c>
       <c r="E87">
-        <v>-23.8783346633244</v>
+        <v>-23.38368719453732</v>
       </c>
       <c r="F87">
-        <v>5.455454438802851</v>
+        <v>6.495690058746775</v>
       </c>
       <c r="G87">
-        <v>-10.48251885248877</v>
+        <v>-10.95466156881324</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.677310073951801</v>
       </c>
       <c r="E88">
-        <v>-25.60671016899709</v>
+        <v>-25.32525949714744</v>
       </c>
       <c r="F88">
-        <v>5.479195448567085</v>
+        <v>6.750689709820158</v>
       </c>
       <c r="G88">
-        <v>-8.676200800906193</v>
+        <v>-10.77216660577754</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.634979484480743</v>
       </c>
       <c r="E89">
-        <v>-25.75872185669714</v>
+        <v>-25.66990127930436</v>
       </c>
       <c r="F89">
-        <v>5.820550744647511</v>
+        <v>6.700422719083479</v>
       </c>
       <c r="G89">
-        <v>-8.982862776695246</v>
+        <v>-10.665709578958</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.557794927177082</v>
       </c>
       <c r="E90">
-        <v>-29.42048783867005</v>
+        <v>-28.79167503124571</v>
       </c>
       <c r="F90">
-        <v>6.152464309070828</v>
+        <v>6.858922537935136</v>
       </c>
       <c r="G90">
-        <v>-9.194240407142438</v>
+        <v>-10.06326721083566</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.449722801524492</v>
       </c>
       <c r="E91">
-        <v>-29.60049009409378</v>
+        <v>-30.06669221851711</v>
       </c>
       <c r="F91">
-        <v>6.250446918943565</v>
+        <v>6.777151078135185</v>
       </c>
       <c r="G91">
-        <v>-8.851437893978604</v>
+        <v>-10.19532780986024</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.301481629518053</v>
       </c>
       <c r="E92">
-        <v>-30.96731194109485</v>
+        <v>-31.04967427487752</v>
       </c>
       <c r="F92">
-        <v>4.807737399205862</v>
+        <v>6.575112268592386</v>
       </c>
       <c r="G92">
-        <v>-8.603267040008852</v>
+        <v>-10.80673155879158</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.113961688738927</v>
       </c>
       <c r="E93">
-        <v>-34.3225771571124</v>
+        <v>-33.3424836592284</v>
       </c>
       <c r="F93">
-        <v>5.422994033756749</v>
+        <v>6.527328723329299</v>
       </c>
       <c r="G93">
-        <v>-9.450755200825387</v>
+        <v>-10.4999011899764</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.875250129799152</v>
       </c>
       <c r="E94">
-        <v>-35.58694966375826</v>
+        <v>-35.24033302961639</v>
       </c>
       <c r="F94">
-        <v>5.4244884085514</v>
+        <v>6.437666235650281</v>
       </c>
       <c r="G94">
-        <v>-9.640667289244446</v>
+        <v>-10.20963860633642</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.587763197828346</v>
       </c>
       <c r="E95">
-        <v>-37.87833657323038</v>
+        <v>-38.37822539470939</v>
       </c>
       <c r="F95">
-        <v>5.188244652212203</v>
+        <v>6.488014406392435</v>
       </c>
       <c r="G95">
-        <v>-8.870714326667089</v>
+        <v>-10.10523754088239</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.241836038529171</v>
       </c>
       <c r="E96">
-        <v>-40.74625774257556</v>
+        <v>-39.13245480111524</v>
       </c>
       <c r="F96">
-        <v>4.98562764222225</v>
+        <v>6.609434843559981</v>
       </c>
       <c r="G96">
-        <v>-8.719660560742161</v>
+        <v>-10.21312395036556</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.850130671803739</v>
       </c>
       <c r="E97">
-        <v>-40.98685119801721</v>
+        <v>-43.03669771986561</v>
       </c>
       <c r="F97">
-        <v>4.903524835461179</v>
+        <v>6.337905949331136</v>
       </c>
       <c r="G97">
-        <v>-8.061652410114855</v>
+        <v>-9.847901668025541</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.408185412722538</v>
       </c>
       <c r="E98">
-        <v>-44.4400553668912</v>
+        <v>-45.09719930536786</v>
       </c>
       <c r="F98">
-        <v>5.024444938717434</v>
+        <v>6.250271305054171</v>
       </c>
       <c r="G98">
-        <v>-7.56906886901426</v>
+        <v>-10.59356426292718</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.945767289390608</v>
       </c>
       <c r="E99">
-        <v>-48.0980948800029</v>
+        <v>-47.27143658300054</v>
       </c>
       <c r="F99">
-        <v>4.580017543441472</v>
+        <v>6.185171567602963</v>
       </c>
       <c r="G99">
-        <v>-9.639264014026722</v>
+        <v>-10.0059966121127</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.457983500106084</v>
       </c>
       <c r="E100">
-        <v>-49.25148423532387</v>
+        <v>-48.95480892906022</v>
       </c>
       <c r="F100">
-        <v>4.603688970343871</v>
+        <v>5.741879035668836</v>
       </c>
       <c r="G100">
-        <v>-7.368177294217275</v>
+        <v>-9.792516026897367</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.998976138591396</v>
       </c>
       <c r="E101">
-        <v>-52.39674751221562</v>
+        <v>-51.95148899420057</v>
       </c>
       <c r="F101">
-        <v>4.403393045816562</v>
+        <v>5.534763990681681</v>
       </c>
       <c r="G101">
-        <v>-9.666708161168504</v>
+        <v>-10.08686573119473</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.543288678174453</v>
       </c>
       <c r="E102">
-        <v>-54.60859782906019</v>
+        <v>-54.75544759423489</v>
       </c>
       <c r="F102">
-        <v>3.41982272642854</v>
+        <v>5.456176775178093</v>
       </c>
       <c r="G102">
-        <v>-8.475204796325563</v>
+        <v>-10.07959741825307</v>
       </c>
     </row>
   </sheetData>
